--- a/grupos/1BV - Estadisticos 20221.xlsx
+++ b/grupos/1BV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -92,6 +92,9 @@
     <t>GUERRA RIVERA CLAUDIA PAOLA</t>
   </si>
   <si>
+    <t>HERNANDEZ CADENA DANA PAOLA</t>
+  </si>
+  <si>
     <t>HERNANDEZ ROJAS LILIANA</t>
   </si>
   <si>
@@ -101,9 +104,6 @@
     <t>JIMENEZ COLMENARES ROSARIO DE JESUS</t>
   </si>
   <si>
-    <t>MARTINEZ PEREZ KATIA GUADALUPE</t>
-  </si>
-  <si>
     <t>MARTINEZ RODRIGUEZ EVIAN ISSAIAS</t>
   </si>
   <si>
@@ -278,109 +278,112 @@
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>CADENA</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
     <t>JORGE</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ESTEPHANY SOPHIA</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CLARA DE VANI</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>EVIAN ISSAIAS</t>
+  </si>
+  <si>
+    <t>VALERIA DANAY</t>
+  </si>
+  <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ARAWY</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>EMILIANO DE JESUS</t>
+  </si>
+  <si>
+    <t>CRISTIAN LEOBARDO</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARCOS</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ESTEPHANY SOPHIA</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CLARA DE VANI</t>
-  </si>
-  <si>
-    <t>LILIANA</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>KATIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>EVIAN ISSAIAS</t>
-  </si>
-  <si>
-    <t>VALERIA DANAY</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ARAWY</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>EMILIANO DE JESUS</t>
-  </si>
-  <si>
-    <t>CRISTIAN LEOBARDO</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
   </si>
   <si>
     <t>PERIAÑEZ</t>
@@ -1901,16 +1904,16 @@
         <v>-1</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="E16">
         <v>-1</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1955,16 +1958,16 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="W16">
         <v>-1</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1972,19 +1975,19 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>-1</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17">
         <v>6</v>
@@ -2026,19 +2029,19 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>-1</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -2049,22 +2052,22 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2103,22 +2106,22 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2126,22 +2129,22 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -2180,22 +2183,22 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -3649,22 +3652,22 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>61.76</v>
       </c>
       <c r="G2">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>32.35</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3713,22 +3716,22 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>70.59</v>
       </c>
       <c r="G4">
-        <v>29.41</v>
+        <v>26.47</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3834,7 +3837,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4083,7 +4086,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920213</v>
+        <v>22330051920423</v>
       </c>
       <c r="B13" t="s">
         <v>70</v>
@@ -4103,7 +4106,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920213</v>
+        <v>22330051920423</v>
       </c>
       <c r="B14" t="s">
         <v>70</v>
@@ -4115,15 +4118,15 @@
         <v>102</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920213</v>
+        <v>22330051920423</v>
       </c>
       <c r="B15" t="s">
         <v>70</v>
@@ -4135,164 +4138,164 @@
         <v>102</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920374</v>
+        <v>22330051920423</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920361</v>
+        <v>22330051920423</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920361</v>
+        <v>22330051920423</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920361</v>
+        <v>22330051920213</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920361</v>
+        <v>22330051920213</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>22330051920215</v>
+        <v>22330051920213</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>22330051920215</v>
+        <v>22330051920374</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>22330051920216</v>
+        <v>22330051920215</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -4303,76 +4306,76 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>22330051920218</v>
+        <v>22330051920215</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>22330051920218</v>
+        <v>22330051920216</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>22330051920217</v>
+        <v>22330051920218</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>22330051920217</v>
+        <v>22330051920218</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E27" t="s">
         <v>6</v>
@@ -4383,62 +4386,62 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>22330051920317</v>
+        <v>22330051920217</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>22330051920421</v>
+        <v>22330051920217</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>22330051920421</v>
+        <v>22330051920317</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4455,89 +4458,129 @@
         <v>110</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>22330051920224</v>
+        <v>22330051920421</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F32" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>22330051920365</v>
+        <v>22330051920421</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>22330051920365</v>
+        <v>22330051920224</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E34" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
+        <v>22330051920365</v>
+      </c>
+      <c r="B35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" t="s">
+        <v>95</v>
+      </c>
+      <c r="D35" t="s">
+        <v>112</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>22330051920365</v>
+      </c>
+      <c r="B36" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" t="s">
+        <v>112</v>
+      </c>
+      <c r="E36" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
         <v>22330051920229</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B37" t="s">
         <v>80</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C37" t="s">
         <v>96</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D37" t="s">
         <v>113</v>
       </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="E37" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" t="s">
         <v>56</v>
       </c>
     </row>
@@ -4574,33 +4617,33 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920379</v>
+        <v>22330051920423</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920361</v>
+        <v>22330051920379</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -4631,10 +4674,10 @@
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -4784,10 +4827,10 @@
         <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -4869,10 +4912,10 @@
         <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4886,10 +4929,10 @@
         <v>115</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4903,10 +4946,10 @@
         <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4923,7 +4966,7 @@
         <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4937,10 +4980,10 @@
         <v>118</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4954,10 +4997,10 @@
         <v>119</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4971,10 +5014,10 @@
         <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4988,10 +5031,10 @@
         <v>120</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5008,7 +5051,7 @@
         <v>96</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5019,13 +5062,13 @@
         <v>22330051920220</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s">
         <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5036,13 +5079,13 @@
         <v>22330051920221</v>
       </c>
       <c r="B29" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5053,13 +5096,13 @@
         <v>22330051920222</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5070,13 +5113,13 @@
         <v>22330051920223</v>
       </c>
       <c r="B31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -5087,13 +5130,13 @@
         <v>22330051920225</v>
       </c>
       <c r="B32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
         <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -5107,10 +5150,10 @@
         <v>85</v>
       </c>
       <c r="C33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -5121,13 +5164,13 @@
         <v>22330051920228</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -5138,13 +5181,13 @@
         <v>22330051920227</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D35" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5287,10 +5330,10 @@
         <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -5356,10 +5399,10 @@
         <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -5399,13 +5442,13 @@
         <v>22330051920221</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -5422,13 +5465,13 @@
         <v>22330051920222</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>

--- a/grupos/1BV - Estadisticos 20221.xlsx
+++ b/grupos/1BV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -185,21 +185,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -233,250 +233,250 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>RONZON</t>
+  </si>
+  <si>
+    <t>USCANGA</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CADENA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ESTEPHANY SOPHIA</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CLARA DE VANI</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
+    <t>EVIAN ISSAIAS</t>
+  </si>
+  <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ARAWY</t>
+  </si>
+  <si>
+    <t>EMILIANO DE JESUS</t>
+  </si>
+  <si>
+    <t>CRISTIAN LEOBARDO</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARCOS</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>MEDINA</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>RONZON</t>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PERIAÑEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>SILVESTRE</t>
   </si>
   <si>
-    <t>USCANGA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>JORGE</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ESTEPHANY SOPHIA</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CLARA DE VANI</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>LILIANA</t>
+    <t>COLMENARES</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>------</t>
+  </si>
+  <si>
+    <t>MERLIN</t>
+  </si>
+  <si>
+    <t>MONTES</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>SAIRA</t>
+  </si>
+  <si>
+    <t>JHESU ALEXIS</t>
+  </si>
+  <si>
+    <t>KARYME CONCEPCION</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
   </si>
   <si>
     <t>KARLA YARITZY</t>
   </si>
   <si>
-    <t>EVIAN ISSAIAS</t>
+    <t>ROSARIO DE JESUS</t>
   </si>
   <si>
     <t>VALERIA DANAY</t>
   </si>
   <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
     <t>JESUS ALEJANDRO</t>
   </si>
   <si>
-    <t>ARAWY</t>
+    <t>DEMY</t>
+  </si>
+  <si>
+    <t>ALBERTO</t>
+  </si>
+  <si>
+    <t>MARIELA</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
   </si>
   <si>
     <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>EMILIANO DE JESUS</t>
-  </si>
-  <si>
-    <t>CRISTIAN LEOBARDO</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PERIAÑEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>COLMENARES</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>MERLIN</t>
-  </si>
-  <si>
-    <t>MONTES</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>SAIRA</t>
-  </si>
-  <si>
-    <t>JHESU ALEXIS</t>
-  </si>
-  <si>
-    <t>KARYME CONCEPCION</t>
-  </si>
-  <si>
-    <t>CLAUDIA PAOLA</t>
-  </si>
-  <si>
-    <t>ROSARIO DE JESUS</t>
-  </si>
-  <si>
-    <t>DEMY</t>
-  </si>
-  <si>
-    <t>ALBERTO</t>
-  </si>
-  <si>
-    <t>MARIELA</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
   </si>
   <si>
     <t>ANGELA</t>
@@ -980,10 +980,10 @@
         <v>-1</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -998,10 +998,10 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -1034,10 +1034,10 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -1072,16 +1072,16 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1108,7 +1108,7 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -1149,16 +1149,16 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1194,7 +1194,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1226,16 +1226,16 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1265,10 +1265,10 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1303,16 +1303,16 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1345,7 +1345,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1383,13 +1383,13 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1419,13 +1419,13 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1457,16 +1457,16 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1502,7 +1502,7 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -1522,7 +1522,7 @@
         <v>6</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F11">
         <v>8</v>
@@ -1537,13 +1537,13 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1573,13 +1573,13 @@
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1614,13 +1614,13 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1650,7 +1650,7 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1688,16 +1688,16 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1730,10 +1730,10 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -1750,13 +1750,13 @@
         <v>-1</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E14">
         <v>5</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -1768,13 +1768,13 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1804,13 +1804,13 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>5</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1842,16 +1842,16 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1878,13 +1878,13 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>8</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1904,13 +1904,13 @@
         <v>-1</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -1922,13 +1922,13 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1958,13 +1958,13 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>-1</v>
@@ -1984,7 +1984,7 @@
         <v>8</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>7</v>
@@ -1999,13 +1999,13 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2035,10 +2035,10 @@
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -2061,7 +2061,7 @@
         <v>6</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F18">
         <v>8</v>
@@ -2073,16 +2073,16 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2109,13 +2109,13 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>6</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -2150,16 +2150,16 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2186,16 +2186,16 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>7</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F20">
         <v>9</v>
@@ -2230,13 +2230,13 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2266,10 +2266,10 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2292,7 +2292,7 @@
         <v>8</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -2304,16 +2304,16 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2340,16 +2340,16 @@
         <v>6</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -2366,7 +2366,7 @@
         <v>-1</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <v>9</v>
@@ -2384,13 +2384,13 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2420,13 +2420,13 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2446,7 +2446,7 @@
         <v>8</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F23">
         <v>8</v>
@@ -2461,13 +2461,13 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2500,7 +2500,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2535,16 +2535,16 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2571,16 +2571,16 @@
         <v>9</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>10</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2600,7 +2600,7 @@
         <v>8</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F25">
         <v>8</v>
@@ -2612,16 +2612,16 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2648,16 +2648,16 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>8</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2689,16 +2689,16 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2725,13 +2725,13 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2766,16 +2766,16 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2805,13 +2805,13 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>9</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2843,16 +2843,16 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2879,16 +2879,16 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -2920,16 +2920,16 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2959,7 +2959,7 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -2982,10 +2982,10 @@
         <v>9</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F30">
         <v>8</v>
@@ -2997,16 +2997,16 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3033,16 +3033,16 @@
         <v>-1</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -3062,7 +3062,7 @@
         <v>6</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F31">
         <v>7</v>
@@ -3074,16 +3074,16 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3113,10 +3113,10 @@
         <v>6</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -3151,16 +3151,16 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3190,7 +3190,7 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3228,16 +3228,16 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3267,13 +3267,13 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y33">
         <v>8</v>
@@ -3293,7 +3293,7 @@
         <v>7</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F34">
         <v>9</v>
@@ -3308,13 +3308,13 @@
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3344,10 +3344,10 @@
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X34">
         <v>9</v>
@@ -3382,16 +3382,16 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3421,7 +3421,7 @@
         <v>10</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>10</v>
@@ -3459,16 +3459,16 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3495,7 +3495,7 @@
         <v>8</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V36">
         <v>8</v>
@@ -3504,7 +3504,7 @@
         <v>9</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y36">
         <v>7</v>
@@ -3539,13 +3539,13 @@
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3575,10 +3575,10 @@
         <v>-1</v>
       </c>
       <c r="V37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>8</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -3649,19 +3649,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>61.76</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="G2">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="I2">
         <v>12</v>
@@ -3672,7 +3672,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3681,30 +3681,30 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>64.70999999999999</v>
+        <v>70.59</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>26.47</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>35.29</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3713,30 +3713,30 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>70.59</v>
+        <v>76.47</v>
       </c>
       <c r="G4">
-        <v>26.47</v>
+        <v>11.76</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>2.94</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -3745,30 +3745,30 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>76.47</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G5">
         <v>11.76</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>11.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -3777,25 +3777,25 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>94.12</v>
+      </c>
+      <c r="G6">
+        <v>5.88</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>85.29000000000001</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>7.2</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>14.71</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3812,22 +3812,22 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>94.12</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="H7">
         <v>8.199999999999999</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3837,7 +3837,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3872,13 +3872,13 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>55</v>
@@ -3886,219 +3886,219 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920362</v>
+        <v>22330051920393</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920362</v>
+        <v>22330051920210</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920393</v>
+        <v>22330051920394</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920210</v>
+        <v>22330051920379</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920210</v>
+        <v>22330051920379</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920394</v>
+        <v>22330051920423</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920379</v>
+        <v>22330051920423</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920379</v>
+        <v>22330051920423</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920379</v>
+        <v>22330051920213</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920379</v>
+        <v>22330051920213</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920423</v>
+        <v>22330051920215</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
         <v>55</v>
@@ -4106,482 +4106,102 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920423</v>
+        <v>22330051920218</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920423</v>
+        <v>22330051920217</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
         <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920423</v>
+        <v>22330051920421</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920423</v>
+        <v>22330051920365</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920423</v>
+        <v>22330051920229</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
         <v>102</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920213</v>
-      </c>
-      <c r="B19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920213</v>
-      </c>
-      <c r="B20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" t="s">
-        <v>103</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920213</v>
-      </c>
-      <c r="B21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920374</v>
-      </c>
-      <c r="B22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" t="s">
-        <v>104</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920215</v>
-      </c>
-      <c r="B23" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" t="s">
-        <v>105</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920215</v>
-      </c>
-      <c r="B24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920216</v>
-      </c>
-      <c r="B25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" t="s">
-        <v>106</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920218</v>
-      </c>
-      <c r="B26" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" t="s">
-        <v>107</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920218</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27" t="s">
-        <v>107</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920217</v>
-      </c>
-      <c r="B28" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" t="s">
-        <v>108</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920217</v>
-      </c>
-      <c r="B29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" t="s">
-        <v>108</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920317</v>
-      </c>
-      <c r="B30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" t="s">
-        <v>109</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920421</v>
-      </c>
-      <c r="B31" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" t="s">
-        <v>93</v>
-      </c>
-      <c r="D31" t="s">
-        <v>110</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920421</v>
-      </c>
-      <c r="B32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" t="s">
-        <v>93</v>
-      </c>
-      <c r="D32" t="s">
-        <v>110</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920421</v>
-      </c>
-      <c r="B33" t="s">
-        <v>77</v>
-      </c>
-      <c r="C33" t="s">
-        <v>93</v>
-      </c>
-      <c r="D33" t="s">
-        <v>110</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920224</v>
-      </c>
-      <c r="B34" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" t="s">
-        <v>111</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920365</v>
-      </c>
-      <c r="B35" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" t="s">
-        <v>95</v>
-      </c>
-      <c r="D35" t="s">
-        <v>112</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920365</v>
-      </c>
-      <c r="B36" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" t="s">
-        <v>95</v>
-      </c>
-      <c r="D36" t="s">
-        <v>112</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920229</v>
-      </c>
-      <c r="B37" t="s">
-        <v>80</v>
-      </c>
-      <c r="C37" t="s">
-        <v>96</v>
-      </c>
-      <c r="D37" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -4623,13 +4243,13 @@
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4640,64 +4260,64 @@
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920362</v>
+        <v>22330051920213</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920213</v>
+        <v>22330051920362</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920421</v>
+        <v>22330051920393</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4708,95 +4328,95 @@
         <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920215</v>
+        <v>22330051920394</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920218</v>
+        <v>22330051920215</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920217</v>
+        <v>22330051920218</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920365</v>
+        <v>22330051920217</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920393</v>
+        <v>22330051920421</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4804,16 +4424,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920394</v>
+        <v>22330051920365</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4821,16 +4441,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920374</v>
+        <v>22330051920229</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -4838,81 +4458,81 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920216</v>
+        <v>22330051920392</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920317</v>
+        <v>22330051920205</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920224</v>
+        <v>22330051920206</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920229</v>
+        <v>22330051920207</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920392</v>
+        <v>22330051920209</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
         <v>140</v>
@@ -4923,13 +4543,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920205</v>
+        <v>22330051920211</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
         <v>141</v>
@@ -4940,13 +4560,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920206</v>
+        <v>22330051920212</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
         <v>142</v>
@@ -4957,13 +4577,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920207</v>
+        <v>22330051920374</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
         <v>143</v>
@@ -4974,13 +4594,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920209</v>
+        <v>22330051920214</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D23" t="s">
         <v>144</v>
@@ -4991,13 +4611,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920211</v>
+        <v>22330051920216</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -5008,13 +4628,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920212</v>
+        <v>22330051920317</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
         <v>146</v>
@@ -5025,13 +4645,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920214</v>
+        <v>22330051920219</v>
       </c>
       <c r="B26" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
         <v>147</v>
@@ -5042,13 +4662,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920219</v>
+        <v>22330051920220</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
         <v>148</v>
@@ -5059,13 +4679,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920220</v>
+        <v>22330051920221</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
         <v>149</v>
@@ -5076,13 +4696,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920221</v>
+        <v>22330051920222</v>
       </c>
       <c r="B29" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D29" t="s">
         <v>150</v>
@@ -5093,13 +4713,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920222</v>
+        <v>22330051920223</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D30" t="s">
         <v>151</v>
@@ -5110,13 +4730,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920223</v>
+        <v>22330051920224</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
         <v>152</v>
@@ -5130,10 +4750,10 @@
         <v>22330051920225</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
         <v>153</v>
@@ -5147,10 +4767,10 @@
         <v>22330051920226</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
         <v>154</v>
@@ -5164,10 +4784,10 @@
         <v>22330051920228</v>
       </c>
       <c r="B34" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C34" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D34" t="s">
         <v>155</v>
@@ -5181,10 +4801,10 @@
         <v>22330051920227</v>
       </c>
       <c r="B35" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C35" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D35" t="s">
         <v>156</v>
@@ -5200,7 +4820,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5232,19 +4852,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920216</v>
+        <v>22330051920362</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>55</v>
@@ -5255,22 +4875,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920216</v>
+        <v>22330051920362</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5278,22 +4898,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920217</v>
+        <v>22330051920213</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5301,22 +4921,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920217</v>
+        <v>22330051920213</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5324,88 +4944,88 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920205</v>
+        <v>22330051920215</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920393</v>
+        <v>22330051920215</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>56</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920394</v>
+        <v>22330051920205</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>56</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920374</v>
+        <v>22330051920393</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>55</v>
@@ -5416,19 +5036,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920317</v>
+        <v>22330051920394</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>55</v>
@@ -5439,22 +5059,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920221</v>
+        <v>22330051920216</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C11" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5462,70 +5082,139 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920222</v>
+        <v>22330051920217</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920224</v>
+        <v>22330051920221</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920229</v>
+        <v>22330051920222</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>56</v>
       </c>
       <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920421</v>
+      </c>
+      <c r="B15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920224</v>
+      </c>
+      <c r="B16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920229</v>
+      </c>
+      <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20221.xlsx
+++ b/grupos/1BV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -1007,7 +1007,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1084,7 +1084,7 @@
         <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1161,7 +1161,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1197,7 +1197,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1238,7 +1238,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1315,7 +1315,7 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1351,7 +1351,7 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1392,7 +1392,7 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1428,7 +1428,7 @@
         <v>6</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1469,7 +1469,7 @@
         <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1546,7 +1546,7 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1623,7 +1623,7 @@
         <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1700,7 +1700,7 @@
         <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1736,7 +1736,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1777,7 +1777,7 @@
         <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1854,7 +1854,7 @@
         <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -2008,7 +2008,7 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2044,7 +2044,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2085,7 +2085,7 @@
         <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2198,7 +2198,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2239,7 +2239,7 @@
         <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2316,7 +2316,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2393,7 +2393,7 @@
         <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2429,7 +2429,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2470,7 +2470,7 @@
         <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2547,7 +2547,7 @@
         <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2583,7 +2583,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2624,7 +2624,7 @@
         <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2660,7 +2660,7 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2701,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2737,7 +2737,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2778,7 +2778,7 @@
         <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2855,7 +2855,7 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2932,7 +2932,7 @@
         <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3009,7 +3009,7 @@
         <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3086,7 +3086,7 @@
         <v>6</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3122,7 +3122,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3163,7 +3163,7 @@
         <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3199,7 +3199,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3240,7 +3240,7 @@
         <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3276,7 +3276,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3317,7 +3317,7 @@
         <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3394,7 +3394,7 @@
         <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3430,7 +3430,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3471,7 +3471,7 @@
         <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3507,7 +3507,7 @@
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3548,7 +3548,7 @@
         <v>8</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3584,7 +3584,7 @@
         <v>8</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3681,19 +3681,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>70.59</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="G3">
-        <v>26.47</v>
+        <v>32.35</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -4820,7 +4820,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4898,22 +4898,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920213</v>
+        <v>22330051920215</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -4921,62 +4921,62 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920213</v>
+        <v>22330051920215</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920215</v>
+        <v>22330051920224</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920215</v>
+        <v>22330051920224</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5174,47 +5174,24 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920224</v>
+        <v>22330051920229</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920229</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20221.xlsx
+++ b/grupos/1BV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -992,7 +992,7 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1004,7 +1004,7 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -1028,7 +1028,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -1069,7 +1069,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>6</v>
@@ -1146,7 +1146,7 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -1223,7 +1223,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>10</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>10</v>
@@ -1300,7 +1300,7 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>10</v>
@@ -1336,7 +1336,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -1377,7 +1377,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1413,7 +1413,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1454,7 +1454,7 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>8</v>
@@ -1490,7 +1490,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1531,7 +1531,7 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1608,7 +1608,7 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1685,7 +1685,7 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <v>10</v>
@@ -1839,7 +1839,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>10</v>
@@ -2070,7 +2070,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>10</v>
@@ -2147,7 +2147,7 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>8</v>
@@ -2224,7 +2224,7 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2301,7 +2301,7 @@
         <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -2337,7 +2337,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>6</v>
@@ -2378,7 +2378,7 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2414,7 +2414,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2455,7 +2455,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2532,7 +2532,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
         <v>10</v>
@@ -2609,7 +2609,7 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>5</v>
@@ -2645,7 +2645,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U25">
         <v>6</v>
@@ -2686,7 +2686,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <v>10</v>
@@ -2763,7 +2763,7 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>8</v>
@@ -2799,7 +2799,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>8</v>
@@ -2840,7 +2840,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
         <v>10</v>
@@ -2917,7 +2917,7 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
         <v>10</v>
@@ -2953,7 +2953,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>10</v>
@@ -3071,7 +3071,7 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -3148,7 +3148,7 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
         <v>10</v>
@@ -3225,7 +3225,7 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>10</v>
@@ -3302,7 +3302,7 @@
         <v>5</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3379,7 +3379,7 @@
         <v>9</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>10</v>
@@ -3415,7 +3415,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>10</v>
@@ -3456,7 +3456,7 @@
         <v>7</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I36">
         <v>10</v>
@@ -3533,7 +3533,7 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -3713,19 +3713,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>76.47</v>
+        <v>70.59</v>
       </c>
       <c r="G4">
-        <v>11.76</v>
+        <v>17.65</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>4</v>
@@ -4820,7 +4820,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4852,16 +4852,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920362</v>
+        <v>22330051920215</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4875,16 +4875,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920362</v>
+        <v>22330051920215</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4898,39 +4898,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920215</v>
+        <v>22330051920216</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920215</v>
+        <v>22330051920216</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5059,68 +5059,68 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920216</v>
+        <v>22330051920217</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920217</v>
+        <v>22330051920317</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920221</v>
+        <v>22330051920222</v>
       </c>
       <c r="B13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5128,70 +5128,47 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920222</v>
+        <v>22330051920421</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920421</v>
+        <v>22330051920229</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920229</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20221.xlsx
+++ b/grupos/1BV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -242,238 +242,238 @@
     <t>MORA</t>
   </si>
   <si>
+    <t>USCANGA</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CADENA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ESTEPHANY SOPHIA</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CLARA DE VANI</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
+    <t>EVIAN ISSAIAS</t>
+  </si>
+  <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>EMILIANO DE JESUS</t>
+  </si>
+  <si>
+    <t>CRISTIAN LEOBARDO</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARCOS</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PERIAÑEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>RONZON</t>
   </si>
   <si>
-    <t>USCANGA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>COLMENARES</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
   </si>
   <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ESTEPHANY SOPHIA</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CLARA DE VANI</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>LILIANA</t>
-  </si>
-  <si>
-    <t>EVIAN ISSAIAS</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
+    <t>------</t>
+  </si>
+  <si>
+    <t>MERLIN</t>
+  </si>
+  <si>
+    <t>MONTES</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>SAIRA</t>
+  </si>
+  <si>
+    <t>JHESU ALEXIS</t>
+  </si>
+  <si>
+    <t>KARYME CONCEPCION</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>ROSARIO DE JESUS</t>
+  </si>
+  <si>
+    <t>VALERIA DANAY</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>DEMY</t>
+  </si>
+  <si>
+    <t>ALBERTO</t>
+  </si>
+  <si>
+    <t>MARIELA</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
   </si>
   <si>
     <t>ARAWY</t>
-  </si>
-  <si>
-    <t>EMILIANO DE JESUS</t>
-  </si>
-  <si>
-    <t>CRISTIAN LEOBARDO</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PERIAÑEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>COLMENARES</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>MERLIN</t>
-  </si>
-  <si>
-    <t>MONTES</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>SAIRA</t>
-  </si>
-  <si>
-    <t>JHESU ALEXIS</t>
-  </si>
-  <si>
-    <t>KARYME CONCEPCION</t>
-  </si>
-  <si>
-    <t>CLAUDIA PAOLA</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>ROSARIO DE JESUS</t>
-  </si>
-  <si>
-    <t>VALERIA DANAY</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>DEMY</t>
-  </si>
-  <si>
-    <t>ALBERTO</t>
-  </si>
-  <si>
-    <t>MARIELA</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
   </si>
   <si>
     <t>MICHELLE</t>
@@ -1898,7 +1898,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C16">
         <v>-1</v>
@@ -1913,10 +1913,10 @@
         <v>6</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -1931,7 +1931,7 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1952,7 +1952,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -1967,7 +1967,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1975,7 +1975,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C17">
         <v>-1</v>
@@ -1993,7 +1993,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2029,7 +2029,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2976,7 +2976,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>9</v>
@@ -2994,7 +2994,7 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
         <v>10</v>
@@ -3030,7 +3030,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>10</v>
@@ -3681,13 +3681,13 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>64.70999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G3">
         <v>32.35</v>
@@ -3696,10 +3696,10 @@
         <v>6.7</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3713,25 +3713,25 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>70.59</v>
+        <v>76.47</v>
       </c>
       <c r="G4">
-        <v>17.65</v>
+        <v>20.59</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>11.76</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3837,7 +3837,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3872,10 +3872,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -3892,10 +3892,10 @@
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -3912,10 +3912,10 @@
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -3932,10 +3932,10 @@
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -3952,10 +3952,10 @@
         <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -3972,10 +3972,10 @@
         <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -3992,21 +3992,21 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920423</v>
+        <v>22330051920213</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
@@ -4015,7 +4015,7 @@
         <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -4026,56 +4026,56 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920423</v>
+        <v>22330051920215</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
         <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920213</v>
+        <v>22330051920218</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
         <v>96</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920213</v>
+        <v>22330051920217</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -4086,16 +4086,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920215</v>
+        <v>22330051920365</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -4106,101 +4106,21 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920218</v>
+        <v>22330051920229</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920217</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920421</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920365</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" t="s">
-        <v>101</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920229</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4237,64 +4157,64 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920423</v>
+        <v>22330051920379</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920379</v>
+        <v>22330051920362</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920213</v>
+        <v>22330051920393</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920362</v>
+        <v>22330051920210</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
         <v>90</v>
@@ -4305,13 +4225,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920393</v>
+        <v>22330051920394</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
         <v>91</v>
@@ -4322,16 +4242,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920210</v>
+        <v>22330051920423</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -4339,16 +4259,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920394</v>
+        <v>22330051920213</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4362,10 +4282,10 @@
         <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4379,10 +4299,10 @@
         <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4396,10 +4316,10 @@
         <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4407,16 +4327,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920421</v>
+        <v>22330051920365</v>
       </c>
       <c r="B12" t="s">
         <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4424,16 +4344,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920365</v>
+        <v>22330051920229</v>
       </c>
       <c r="B13" t="s">
         <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4441,30 +4361,30 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920229</v>
+        <v>22330051920392</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920392</v>
+        <v>22330051920205</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
         <v>136</v>
@@ -4475,13 +4395,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920205</v>
+        <v>22330051920206</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D16" t="s">
         <v>137</v>
@@ -4492,13 +4412,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920206</v>
+        <v>22330051920207</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
         <v>138</v>
@@ -4509,13 +4429,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920207</v>
+        <v>22330051920209</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
         <v>139</v>
@@ -4526,13 +4446,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920209</v>
+        <v>22330051920211</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
         <v>140</v>
@@ -4543,13 +4463,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920211</v>
+        <v>22330051920212</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
         <v>141</v>
@@ -4560,13 +4480,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920212</v>
+        <v>22330051920374</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
         <v>142</v>
@@ -4577,13 +4497,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920374</v>
+        <v>22330051920214</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
         <v>143</v>
@@ -4594,13 +4514,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920214</v>
+        <v>22330051920216</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
         <v>144</v>
@@ -4611,13 +4531,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920216</v>
+        <v>22330051920317</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -4628,13 +4548,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920317</v>
+        <v>22330051920219</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D25" t="s">
         <v>146</v>
@@ -4645,13 +4565,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920219</v>
+        <v>22330051920220</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
         <v>147</v>
@@ -4662,13 +4582,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920220</v>
+        <v>22330051920221</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
         <v>148</v>
@@ -4679,13 +4599,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920221</v>
+        <v>22330051920222</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
         <v>149</v>
@@ -4696,13 +4616,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920222</v>
+        <v>22330051920223</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C29" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
         <v>150</v>
@@ -4713,13 +4633,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920223</v>
+        <v>22330051920421</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D30" t="s">
         <v>151</v>
@@ -4733,10 +4653,10 @@
         <v>22330051920224</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
         <v>152</v>
@@ -4750,10 +4670,10 @@
         <v>22330051920225</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D32" t="s">
         <v>153</v>
@@ -4767,10 +4687,10 @@
         <v>22330051920226</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D33" t="s">
         <v>154</v>
@@ -4784,10 +4704,10 @@
         <v>22330051920228</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D34" t="s">
         <v>155</v>
@@ -4801,10 +4721,10 @@
         <v>22330051920227</v>
       </c>
       <c r="B35" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D35" t="s">
         <v>156</v>
@@ -4820,7 +4740,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4858,10 +4778,10 @@
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4881,10 +4801,10 @@
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4901,13 +4821,13 @@
         <v>22330051920216</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4924,13 +4844,13 @@
         <v>22330051920216</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4947,10 +4867,10 @@
         <v>22330051920224</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
         <v>152</v>
@@ -4970,10 +4890,10 @@
         <v>22330051920224</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
         <v>152</v>
@@ -4993,13 +4913,13 @@
         <v>22330051920205</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -5019,10 +4939,10 @@
         <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -5042,10 +4962,10 @@
         <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5065,10 +4985,10 @@
         <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -5085,13 +5005,13 @@
         <v>22330051920317</v>
       </c>
       <c r="B12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -5108,13 +5028,13 @@
         <v>22330051920222</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -5128,47 +5048,24 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920421</v>
+        <v>22330051920229</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
         <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920229</v>
-      </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20221.xlsx
+++ b/grupos/1BV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -185,15 +185,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
@@ -215,52 +215,133 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CLARA DE VANI</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARCOS</t>
+  </si>
+  <si>
     <t>ALFONSO</t>
   </si>
   <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
     <t>CHONKOA</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GOMEZ</t>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
     <t>MORA</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PERIAÑEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RONZON</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
     <t>USCANGA</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
     <t>XICALHUA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>SANDOVAL</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>JUAREZ</t>
   </si>
   <si>
     <t>VALLEJO</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>CADENA</t>
@@ -269,6 +350,12 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>COLMENARES</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -278,25 +365,64 @@
     <t>TORRES</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>------</t>
+  </si>
+  <si>
     <t>JUAN</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
+    <t>MERLIN</t>
+  </si>
+  <si>
+    <t>MONTES</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>LORENA</t>
   </si>
   <si>
     <t>ESTEPHANY SOPHIA</t>
   </si>
   <si>
+    <t>SAIRA</t>
+  </si>
+  <si>
     <t>ABRIL</t>
   </si>
   <si>
+    <t>JHESU ALEXIS</t>
+  </si>
+  <si>
     <t>ANDREA</t>
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
   </si>
   <si>
-    <t>CLARA DE VANI</t>
+    <t>KARYME CONCEPCION</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
   </si>
   <si>
     <t>DANA PAOLA</t>
@@ -305,190 +431,64 @@
     <t>LILIANA</t>
   </si>
   <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>ROSARIO DE JESUS</t>
+  </si>
+  <si>
     <t>EVIAN ISSAIAS</t>
   </si>
   <si>
+    <t>VALERIA DANAY</t>
+  </si>
+  <si>
     <t>ANGELES VALERIA</t>
   </si>
   <si>
     <t>MARISOL</t>
   </si>
   <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>DEMY</t>
+  </si>
+  <si>
+    <t>ALBERTO</t>
+  </si>
+  <si>
+    <t>MARIELA</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>ARAWY</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>AMERICA</t>
+  </si>
+  <si>
     <t>EMILIANO DE JESUS</t>
   </si>
   <si>
+    <t>ANDREA JANETH</t>
+  </si>
+  <si>
+    <t>ESTRELLA SARAHI</t>
+  </si>
+  <si>
     <t>CRISTIAN LEOBARDO</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PERIAÑEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RONZON</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>COLMENARES</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>MERLIN</t>
-  </si>
-  <si>
-    <t>MONTES</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>SAIRA</t>
-  </si>
-  <si>
-    <t>JHESU ALEXIS</t>
-  </si>
-  <si>
-    <t>KARYME CONCEPCION</t>
-  </si>
-  <si>
-    <t>CLAUDIA PAOLA</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>ROSARIO DE JESUS</t>
-  </si>
-  <si>
-    <t>VALERIA DANAY</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>DEMY</t>
-  </si>
-  <si>
-    <t>ALBERTO</t>
-  </si>
-  <si>
-    <t>MARIELA</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>ARAWY</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>AMERICA</t>
-  </si>
-  <si>
-    <t>ANDREA JANETH</t>
-  </si>
-  <si>
-    <t>ESTRELLA SARAHI</t>
   </si>
 </sst>
 </file>
@@ -977,7 +977,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -995,7 +995,7 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1031,7 +1031,7 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -1362,7 +1362,7 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -1380,7 +1380,7 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>8</v>
@@ -1416,7 +1416,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1516,7 +1516,7 @@
         <v>5</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -1534,7 +1534,7 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -1570,7 +1570,7 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -1593,7 +1593,7 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -1611,7 +1611,7 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>8</v>
@@ -1647,7 +1647,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>-1</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -1765,7 +1765,7 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1801,7 +1801,7 @@
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1901,7 +1901,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>4</v>
@@ -1919,7 +1919,7 @@
         <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>7</v>
@@ -1955,7 +1955,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -1978,7 +1978,7 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>8</v>
@@ -1996,7 +1996,7 @@
         <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -2032,7 +2032,7 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>6</v>
@@ -2209,7 +2209,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -2227,7 +2227,7 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>5</v>
@@ -2263,7 +2263,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2363,7 +2363,7 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <v>8</v>
@@ -2381,7 +2381,7 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>9</v>
@@ -2417,7 +2417,7 @@
         <v>7</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2440,7 +2440,7 @@
         <v>5</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>8</v>
@@ -2458,7 +2458,7 @@
         <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>7</v>
@@ -2494,7 +2494,7 @@
         <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -3287,7 +3287,7 @@
         <v>5</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D34">
         <v>7</v>
@@ -3305,7 +3305,7 @@
         <v>5</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>5</v>
@@ -3341,7 +3341,7 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>6</v>
@@ -3518,7 +3518,7 @@
         <v>6</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D37">
         <v>6</v>
@@ -3536,7 +3536,7 @@
         <v>6</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J37">
         <v>8</v>
@@ -3572,7 +3572,7 @@
         <v>6</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V37">
         <v>7</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -3649,30 +3649,30 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="G2">
+        <v>32.35</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>64.70999999999999</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>9</v>
-      </c>
-      <c r="I2">
-        <v>12</v>
-      </c>
-      <c r="J2">
-        <v>35.29</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3681,30 +3681,30 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>67.65000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="G3">
-        <v>32.35</v>
+        <v>20.59</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3713,25 +3713,25 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>76.47</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G4">
-        <v>20.59</v>
+        <v>14.71</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3837,7 +3837,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3866,262 +3866,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>22330051920362</v>
+        <v>22330051920379</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920393</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920210</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920394</v>
-      </c>
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920379</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920379</v>
-      </c>
-      <c r="B7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920423</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920213</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920215</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920218</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920217</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920365</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920229</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -4160,214 +3920,214 @@
         <v>22330051920379</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920362</v>
+        <v>22330051920392</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920393</v>
+        <v>22330051920205</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920210</v>
+        <v>22330051920206</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920394</v>
+        <v>22330051920362</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920423</v>
+        <v>22330051920207</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920213</v>
+        <v>22330051920393</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920215</v>
+        <v>22330051920209</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920218</v>
+        <v>22330051920210</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920217</v>
+        <v>22330051920394</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920365</v>
+        <v>22330051920211</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920229</v>
+        <v>22330051920212</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920392</v>
+        <v>22330051920423</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
         <v>135</v>
@@ -4378,13 +4138,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920205</v>
+        <v>22330051920213</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
         <v>136</v>
@@ -4395,13 +4155,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920206</v>
+        <v>22330051920374</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
         <v>137</v>
@@ -4412,13 +4172,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920207</v>
+        <v>22330051920214</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
         <v>138</v>
@@ -4429,13 +4189,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920209</v>
+        <v>22330051920215</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
         <v>139</v>
@@ -4446,13 +4206,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920211</v>
+        <v>22330051920216</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
         <v>140</v>
@@ -4463,13 +4223,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920212</v>
+        <v>22330051920218</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
         <v>141</v>
@@ -4480,13 +4240,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920374</v>
+        <v>22330051920217</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
         <v>142</v>
@@ -4497,13 +4257,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920214</v>
+        <v>22330051920317</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
         <v>143</v>
@@ -4514,13 +4274,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920216</v>
+        <v>22330051920219</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
         <v>144</v>
@@ -4531,13 +4291,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920317</v>
+        <v>22330051920220</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -4548,13 +4308,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920219</v>
+        <v>22330051920221</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
         <v>146</v>
@@ -4565,13 +4325,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920220</v>
+        <v>22330051920222</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
         <v>147</v>
@@ -4582,13 +4342,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920221</v>
+        <v>22330051920223</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
         <v>148</v>
@@ -4599,13 +4359,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920222</v>
+        <v>22330051920421</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
         <v>149</v>
@@ -4616,13 +4376,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920223</v>
+        <v>22330051920224</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
         <v>150</v>
@@ -4633,13 +4393,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920421</v>
+        <v>22330051920225</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="D30" t="s">
         <v>151</v>
@@ -4650,13 +4410,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920224</v>
+        <v>22330051920226</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
         <v>152</v>
@@ -4667,13 +4427,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920225</v>
+        <v>22330051920365</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
         <v>153</v>
@@ -4684,13 +4444,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920226</v>
+        <v>22330051920228</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
         <v>154</v>
@@ -4701,13 +4461,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920228</v>
+        <v>22330051920227</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D34" t="s">
         <v>155</v>
@@ -4718,13 +4478,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920227</v>
+        <v>22330051920229</v>
       </c>
       <c r="B35" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D35" t="s">
         <v>156</v>
@@ -4740,7 +4500,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4772,45 +4532,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920215</v>
+        <v>22330051920423</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920215</v>
+        <v>22330051920423</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4821,19 +4581,19 @@
         <v>22330051920216</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4844,19 +4604,19 @@
         <v>22330051920216</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4864,22 +4624,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920224</v>
+        <v>22330051920218</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4887,22 +4647,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920224</v>
+        <v>22330051920218</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4910,22 +4670,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920205</v>
+        <v>22330051920224</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4933,71 +4693,71 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920393</v>
+        <v>22330051920224</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>150</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>55</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920394</v>
+        <v>22330051920205</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>55</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920217</v>
+        <v>22330051920215</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>55</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -5005,19 +4765,19 @@
         <v>22330051920317</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5028,45 +4788,22 @@
         <v>22330051920222</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13">
         <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920229</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1BV - Estadisticos 20221.xlsx
+++ b/grupos/1BV - Estadisticos 20221.xlsx
@@ -191,16 +191,16 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
+    <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>NC</t>
@@ -1016,10 +1016,10 @@
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1037,7 +1037,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -1093,10 +1093,10 @@
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1111,10 +1111,10 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1170,10 +1170,10 @@
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1247,10 +1247,10 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1265,7 +1265,7 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1324,10 +1324,10 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1401,10 +1401,10 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1422,7 +1422,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>6</v>
@@ -1478,10 +1478,10 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1499,7 +1499,7 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1555,10 +1555,10 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1576,7 +1576,7 @@
         <v>5</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1632,10 +1632,10 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1653,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1709,10 +1709,10 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1727,7 +1727,7 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>9</v>
@@ -1786,10 +1786,10 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1863,10 +1863,10 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1884,7 +1884,7 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1940,10 +1940,10 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1958,10 +1958,10 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -2017,10 +2017,10 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2038,7 +2038,7 @@
         <v>6</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -2094,10 +2094,10 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2112,7 +2112,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2171,10 +2171,10 @@
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2248,10 +2248,10 @@
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2269,7 +2269,7 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2325,10 +2325,10 @@
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2343,7 +2343,7 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2402,10 +2402,10 @@
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2423,7 +2423,7 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2479,10 +2479,10 @@
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2497,10 +2497,10 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2556,10 +2556,10 @@
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2633,10 +2633,10 @@
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2654,7 +2654,7 @@
         <v>8</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -2710,10 +2710,10 @@
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2787,10 +2787,10 @@
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2805,7 +2805,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2864,10 +2864,10 @@
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2941,10 +2941,10 @@
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3018,10 +3018,10 @@
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3095,10 +3095,10 @@
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3116,7 +3116,7 @@
         <v>5</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -3172,10 +3172,10 @@
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3249,10 +3249,10 @@
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3326,10 +3326,10 @@
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3344,10 +3344,10 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>9</v>
@@ -3403,10 +3403,10 @@
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -3421,7 +3421,7 @@
         <v>10</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>10</v>
@@ -3480,10 +3480,10 @@
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -3557,10 +3557,10 @@
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -3704,7 +3704,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3725,7 +3725,7 @@
         <v>14.71</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3736,7 +3736,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -3745,19 +3745,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>88.23999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G5">
-        <v>11.76</v>
+        <v>14.71</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3768,7 +3768,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -3789,7 +3789,7 @@
         <v>5.88</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3800,7 +3800,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -3809,19 +3809,19 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="G7">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4532,22 +4532,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920423</v>
+        <v>22330051920216</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4555,22 +4555,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920423</v>
+        <v>22330051920216</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4578,16 +4578,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920216</v>
+        <v>22330051920218</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4601,16 +4601,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920216</v>
+        <v>22330051920218</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4624,22 +4624,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920218</v>
+        <v>22330051920224</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4647,16 +4647,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920218</v>
+        <v>22330051920224</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4670,22 +4670,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920224</v>
+        <v>22330051920205</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4693,22 +4693,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920224</v>
+        <v>22330051920423</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4716,22 +4716,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920205</v>
+        <v>22330051920374</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>5</v>

--- a/grupos/1BV - Estadisticos 20221.xlsx
+++ b/grupos/1BV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -197,10 +197,10 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
     <t>NC</t>
@@ -1013,7 +1013,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>7</v>
@@ -1022,7 +1022,7 @@
         <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -1031,7 +1031,7 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -1090,7 +1090,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>4</v>
@@ -1099,7 +1099,7 @@
         <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1117,7 +1117,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1167,7 +1167,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>8</v>
@@ -1176,7 +1176,7 @@
         <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1244,7 +1244,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>7</v>
@@ -1253,7 +1253,7 @@
         <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1321,7 +1321,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>8</v>
@@ -1330,7 +1330,7 @@
         <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1339,7 +1339,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1398,7 +1398,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>7</v>
@@ -1407,7 +1407,7 @@
         <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1416,7 +1416,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1425,7 +1425,7 @@
         <v>8</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1475,7 +1475,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>8</v>
@@ -1484,7 +1484,7 @@
         <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1552,7 +1552,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>7</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1570,7 +1570,7 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -1629,7 +1629,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
         <v>10</v>
@@ -1638,7 +1638,7 @@
         <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1647,7 +1647,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1706,7 +1706,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>9</v>
@@ -1715,7 +1715,7 @@
         <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1783,7 +1783,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1792,7 +1792,7 @@
         <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1860,7 +1860,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
         <v>8</v>
@@ -1869,7 +1869,7 @@
         <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1937,7 +1937,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
         <v>7</v>
@@ -1946,7 +1946,7 @@
         <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1955,7 +1955,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>6</v>
@@ -1964,7 +1964,7 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -2014,7 +2014,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -2023,7 +2023,7 @@
         <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2091,7 +2091,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>5</v>
@@ -2100,7 +2100,7 @@
         <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2168,7 +2168,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>9</v>
@@ -2177,7 +2177,7 @@
         <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2245,7 +2245,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>7</v>
@@ -2254,7 +2254,7 @@
         <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2322,7 +2322,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>9</v>
@@ -2331,7 +2331,7 @@
         <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2340,7 +2340,7 @@
         <v>5</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2399,7 +2399,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>9</v>
@@ -2408,7 +2408,7 @@
         <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2417,7 +2417,7 @@
         <v>7</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2476,7 +2476,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>6</v>
@@ -2485,7 +2485,7 @@
         <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2494,7 +2494,7 @@
         <v>5</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2503,7 +2503,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2553,7 +2553,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>10</v>
@@ -2562,7 +2562,7 @@
         <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>9</v>
@@ -2630,7 +2630,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>8</v>
@@ -2639,7 +2639,7 @@
         <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2648,7 +2648,7 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>8</v>
@@ -2707,7 +2707,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>9</v>
@@ -2716,7 +2716,7 @@
         <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2734,7 +2734,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2784,7 +2784,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>9</v>
@@ -2793,7 +2793,7 @@
         <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2811,7 +2811,7 @@
         <v>9</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2861,7 +2861,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
         <v>7</v>
@@ -2870,7 +2870,7 @@
         <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2879,7 +2879,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>7</v>
@@ -2938,7 +2938,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>9</v>
@@ -2947,7 +2947,7 @@
         <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3015,7 +3015,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>8</v>
@@ -3024,7 +3024,7 @@
         <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3033,7 +3033,7 @@
         <v>6</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V30">
         <v>7</v>
@@ -3092,7 +3092,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>6</v>
@@ -3101,7 +3101,7 @@
         <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3169,7 +3169,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>9</v>
@@ -3178,7 +3178,7 @@
         <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3246,7 +3246,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>9</v>
@@ -3255,7 +3255,7 @@
         <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3323,7 +3323,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
         <v>5</v>
@@ -3332,7 +3332,7 @@
         <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3341,7 +3341,7 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>5</v>
@@ -3400,7 +3400,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
         <v>8</v>
@@ -3409,7 +3409,7 @@
         <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3477,7 +3477,7 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
         <v>9</v>
@@ -3486,7 +3486,7 @@
         <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3495,7 +3495,7 @@
         <v>8</v>
       </c>
       <c r="U36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>8</v>
@@ -3554,7 +3554,7 @@
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P37">
         <v>8</v>
@@ -3563,7 +3563,7 @@
         <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3745,16 +3745,16 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>85.29000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="G5">
-        <v>14.71</v>
+        <v>5.88</v>
       </c>
       <c r="H5">
         <v>8.199999999999999</v>
@@ -3768,7 +3768,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -3777,19 +3777,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="G6">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3800,7 +3800,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -3821,7 +3821,7 @@
         <v>2.94</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4500,7 +4500,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4532,16 +4532,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920216</v>
+        <v>22330051920362</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
         <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4555,16 +4555,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920216</v>
+        <v>22330051920362</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
         <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4578,16 +4578,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920218</v>
+        <v>22330051920216</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4601,16 +4601,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920218</v>
+        <v>22330051920216</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4624,22 +4624,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920224</v>
+        <v>22330051920218</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4647,16 +4647,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920224</v>
+        <v>22330051920218</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4670,22 +4670,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920205</v>
+        <v>22330051920224</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4693,22 +4693,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920423</v>
+        <v>22330051920224</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4716,22 +4716,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920374</v>
+        <v>22330051920205</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4739,22 +4739,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920215</v>
+        <v>22330051920374</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4762,22 +4762,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920317</v>
+        <v>22330051920215</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -4785,24 +4785,47 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
+        <v>22330051920317</v>
+      </c>
+      <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
         <v>22330051920222</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>90</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>117</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>147</v>
       </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
         <v>55</v>
       </c>
-      <c r="G13">
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20221.xlsx
+++ b/grupos/1BV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -185,19 +185,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
     <t>Pesce Bautista Victor Manuel</t>
@@ -1010,7 +1010,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>7</v>
@@ -1025,10 +1025,10 @@
         <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>6</v>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>7</v>
@@ -1102,10 +1102,10 @@
         <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -1120,7 +1120,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1164,7 +1164,7 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1241,7 +1241,7 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>10</v>
@@ -1256,7 +1256,7 @@
         <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -1274,7 +1274,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1318,7 +1318,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>8</v>
@@ -1333,7 +1333,7 @@
         <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1395,7 +1395,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>8</v>
@@ -1410,10 +1410,10 @@
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -1428,7 +1428,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1472,7 +1472,7 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>10</v>
@@ -1487,7 +1487,7 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1505,7 +1505,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1549,7 +1549,7 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -1564,10 +1564,10 @@
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1582,7 +1582,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1626,7 +1626,7 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>9</v>
@@ -1641,7 +1641,7 @@
         <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -1703,7 +1703,7 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>10</v>
@@ -1718,7 +1718,7 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1795,7 +1795,7 @@
         <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -1857,7 +1857,7 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>9</v>
@@ -1872,10 +1872,10 @@
         <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -1934,7 +1934,7 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>9</v>
@@ -1949,7 +1949,7 @@
         <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>6</v>
@@ -1967,7 +1967,7 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2011,7 +2011,7 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -2026,10 +2026,10 @@
         <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -2088,7 +2088,7 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>7</v>
@@ -2103,10 +2103,10 @@
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -2165,7 +2165,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
         <v>8</v>
@@ -2180,7 +2180,7 @@
         <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2198,7 +2198,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2242,7 +2242,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>7</v>
@@ -2257,10 +2257,10 @@
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2275,7 +2275,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2319,7 +2319,7 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>9</v>
@@ -2334,10 +2334,10 @@
         <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2352,7 +2352,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2396,7 +2396,7 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
         <v>8</v>
@@ -2411,10 +2411,10 @@
         <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>9</v>
@@ -2473,7 +2473,7 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>6</v>
@@ -2488,10 +2488,10 @@
         <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -2550,7 +2550,7 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>9</v>
@@ -2565,7 +2565,7 @@
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2583,7 +2583,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2627,7 +2627,7 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>8</v>
@@ -2642,10 +2642,10 @@
         <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>7</v>
@@ -2704,7 +2704,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>8</v>
@@ -2719,7 +2719,7 @@
         <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -2781,7 +2781,7 @@
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
         <v>8</v>
@@ -2796,10 +2796,10 @@
         <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>8</v>
@@ -2814,7 +2814,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2858,7 +2858,7 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
         <v>7</v>
@@ -2873,7 +2873,7 @@
         <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -2891,7 +2891,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2935,7 +2935,7 @@
         <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>10</v>
@@ -2950,7 +2950,7 @@
         <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -3012,7 +3012,7 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
         <v>9</v>
@@ -3027,7 +3027,7 @@
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>6</v>
@@ -3089,7 +3089,7 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>7</v>
@@ -3104,7 +3104,7 @@
         <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>6</v>
@@ -3122,7 +3122,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3166,7 +3166,7 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>10</v>
@@ -3181,10 +3181,10 @@
         <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>10</v>
@@ -3199,7 +3199,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3243,7 +3243,7 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>10</v>
@@ -3258,7 +3258,7 @@
         <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -3276,7 +3276,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3320,7 +3320,7 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
         <v>7</v>
@@ -3335,10 +3335,10 @@
         <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>6</v>
@@ -3397,7 +3397,7 @@
         <v>7</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>10</v>
@@ -3412,7 +3412,7 @@
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3474,7 +3474,7 @@
         <v>9</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O36">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
         <v>8</v>
@@ -3551,7 +3551,7 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
         <v>8</v>
@@ -3566,7 +3566,7 @@
         <v>8</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
         <v>6</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -3649,19 +3649,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>67.65000000000001</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G2">
-        <v>32.35</v>
+        <v>14.71</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3672,7 +3672,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3681,30 +3681,30 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>76.47</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G3">
-        <v>20.59</v>
+        <v>14.71</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3713,19 +3713,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>85.29000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="G4">
-        <v>14.71</v>
+        <v>5.88</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3736,7 +3736,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -3745,19 +3745,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="G5">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3768,7 +3768,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -3780,22 +3780,22 @@
         <v>33</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>97.06</v>
       </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>7.3</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>2.94</v>
-      </c>
-      <c r="H6">
-        <v>8.5</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3881,7 +3881,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4500,7 +4500,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4532,22 +4532,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920362</v>
+        <v>22330051920213</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4555,22 +4555,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920362</v>
+        <v>22330051920213</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4578,22 +4578,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920216</v>
+        <v>22330051920365</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920216</v>
+        <v>22330051920365</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4624,19 +4624,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920218</v>
+        <v>22330051920362</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>56</v>
@@ -4647,19 +4647,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920218</v>
+        <v>22330051920210</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>55</v>
@@ -4670,22 +4670,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920224</v>
+        <v>22330051920374</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4693,22 +4693,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920224</v>
+        <v>22330051920218</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4716,116 +4716,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920205</v>
+        <v>22330051920224</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>55</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920374</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" t="s">
-        <v>137</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920215</v>
-      </c>
-      <c r="B12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" t="s">
-        <v>139</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920317</v>
-      </c>
-      <c r="B13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920222</v>
-      </c>
-      <c r="B14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" t="s">
-        <v>117</v>
-      </c>
-      <c r="D14" t="s">
-        <v>147</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20221.xlsx
+++ b/grupos/1BV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -215,211 +215,211 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARCOS</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>CHONKOA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PERIAÑEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RONZON</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>USCANGA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>CADENA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>COLMENARES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>------</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>MERLIN</t>
+  </si>
+  <si>
+    <t>MONTES</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>ESTEPHANY SOPHIA</t>
+  </si>
+  <si>
+    <t>SAIRA</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>JHESU ALEXIS</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>KARYME CONCEPCION</t>
+  </si>
+  <si>
     <t>CLARA DE VANI</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>CHONKOA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PERIAÑEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RONZON</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>USCANGA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>COLMENARES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>MERLIN</t>
-  </si>
-  <si>
-    <t>MONTES</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>ESTEPHANY SOPHIA</t>
-  </si>
-  <si>
-    <t>SAIRA</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>JHESU ALEXIS</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>KARYME CONCEPCION</t>
   </si>
   <si>
     <t>CLAUDIA PAOLA</t>
@@ -1744,7 +1744,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -1762,7 +1762,7 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
         <v>5</v>
@@ -1780,7 +1780,7 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -1798,7 +1798,7 @@
         <v>5</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
         <v>5</v>
@@ -3780,22 +3780,22 @@
         <v>33</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>97.06</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="H6">
         <v>7.3</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3837,7 +3837,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3862,26 +3862,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920379</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -3917,27 +3897,27 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920379</v>
+        <v>22330051920392</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920392</v>
+        <v>22330051920205</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
         <v>98</v>
@@ -3951,10 +3931,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920205</v>
+        <v>22330051920206</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
         <v>99</v>
@@ -3968,10 +3948,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920206</v>
+        <v>22330051920362</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
         <v>100</v>
@@ -3985,13 +3965,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920362</v>
+        <v>22330051920207</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
         <v>127</v>
@@ -4002,13 +3982,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920207</v>
+        <v>22330051920393</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
         <v>128</v>
@@ -4019,10 +3999,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920393</v>
+        <v>22330051920209</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
         <v>102</v>
@@ -4036,10 +4016,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920209</v>
+        <v>22330051920210</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
         <v>103</v>
@@ -4053,10 +4033,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920210</v>
+        <v>22330051920394</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
         <v>104</v>
@@ -4070,10 +4050,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920394</v>
+        <v>22330051920211</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
         <v>105</v>
@@ -4087,13 +4067,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920211</v>
+        <v>22330051920379</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
         <v>133</v>
@@ -4107,10 +4087,10 @@
         <v>22330051920212</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
         <v>134</v>
@@ -4124,10 +4104,10 @@
         <v>22330051920423</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
         <v>135</v>
@@ -4141,10 +4121,10 @@
         <v>22330051920213</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
         <v>136</v>
@@ -4158,10 +4138,10 @@
         <v>22330051920374</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
         <v>137</v>
@@ -4175,10 +4155,10 @@
         <v>22330051920214</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
         <v>138</v>
@@ -4192,10 +4172,10 @@
         <v>22330051920215</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D18" t="s">
         <v>139</v>
@@ -4209,10 +4189,10 @@
         <v>22330051920216</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
         <v>140</v>
@@ -4226,10 +4206,10 @@
         <v>22330051920218</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
         <v>141</v>
@@ -4243,10 +4223,10 @@
         <v>22330051920217</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
         <v>142</v>
@@ -4260,10 +4240,10 @@
         <v>22330051920317</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
         <v>143</v>
@@ -4277,10 +4257,10 @@
         <v>22330051920219</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
         <v>144</v>
@@ -4294,10 +4274,10 @@
         <v>22330051920220</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -4311,10 +4291,10 @@
         <v>22330051920221</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
         <v>146</v>
@@ -4328,10 +4308,10 @@
         <v>22330051920222</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
         <v>147</v>
@@ -4345,10 +4325,10 @@
         <v>22330051920223</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
         <v>148</v>
@@ -4362,10 +4342,10 @@
         <v>22330051920421</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
         <v>149</v>
@@ -4379,10 +4359,10 @@
         <v>22330051920224</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s">
         <v>150</v>
@@ -4396,10 +4376,10 @@
         <v>22330051920225</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D30" t="s">
         <v>151</v>
@@ -4413,10 +4393,10 @@
         <v>22330051920226</v>
       </c>
       <c r="B31" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
         <v>152</v>
@@ -4430,10 +4410,10 @@
         <v>22330051920365</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
         <v>153</v>
@@ -4447,10 +4427,10 @@
         <v>22330051920228</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
         <v>154</v>
@@ -4464,10 +4444,10 @@
         <v>22330051920227</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D34" t="s">
         <v>155</v>
@@ -4481,10 +4461,10 @@
         <v>22330051920229</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D35" t="s">
         <v>156</v>
@@ -4535,10 +4515,10 @@
         <v>22330051920213</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
         <v>136</v>
@@ -4558,10 +4538,10 @@
         <v>22330051920213</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
         <v>136</v>
@@ -4581,10 +4561,10 @@
         <v>22330051920365</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
         <v>153</v>
@@ -4604,10 +4584,10 @@
         <v>22330051920365</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
         <v>153</v>
@@ -4627,13 +4607,13 @@
         <v>22330051920362</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -4650,13 +4630,13 @@
         <v>22330051920210</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -4673,10 +4653,10 @@
         <v>22330051920374</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
         <v>137</v>
@@ -4696,10 +4676,10 @@
         <v>22330051920218</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
         <v>141</v>
@@ -4719,10 +4699,10 @@
         <v>22330051920224</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
         <v>150</v>
